--- a/static/templates/control_question_template.xlsx
+++ b/static/templates/control_question_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\grc_backend\static\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cydea\grc_backend\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FF14704-2856-4F8F-8414-74E388DB11DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F19E425-8C15-488A-A243-F1635469C8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{F5523B83-E1A5-433A-A3BD-C493FBCEBF4F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F5523B83-E1A5-433A-A3BD-C493FBCEBF4F}"/>
   </bookViews>
   <sheets>
     <sheet name="control_question_template" sheetId="1" r:id="rId1"/>
@@ -593,8 +593,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -694,7 +695,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -800,7 +801,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -942,7 +943,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -952,9 +953,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11746F43-75F6-443F-A11C-606C6ACD3462}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -965,7 +969,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -976,7 +980,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
@@ -987,7 +991,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>6.1</v>
       </c>
       <c r="B4" t="s">
@@ -998,7 +1002,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
@@ -1009,7 +1013,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
@@ -1020,7 +1024,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
@@ -1031,7 +1035,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
@@ -1042,7 +1046,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -1053,7 +1057,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -1064,7 +1068,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" t="s">
@@ -1075,7 +1079,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
@@ -1086,7 +1090,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
@@ -1097,7 +1101,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
@@ -1108,7 +1112,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
@@ -1119,7 +1123,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
@@ -1130,7 +1134,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B17" t="s">
@@ -1141,7 +1145,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B18" t="s">
@@ -1152,7 +1156,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B19" t="s">
@@ -1163,7 +1167,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B20" t="s">
@@ -1174,7 +1178,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B21" t="s">
